--- a/inst/app/metadata/stettehbaah_2024-08-16.xlsx
+++ b/inst/app/metadata/stettehbaah_2024-08-16.xlsx
@@ -1,24 +1,99 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://worldbankgroup-my.sharepoint.com/personal/zprinsloo_worldbank_org/Documents/innovation_hub/InnovationHubDashboard/inst/app/metadata/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_6D68FDCE8F79A89360642C52EAAAD23310C181F4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{924F6C67-2211-4544-B55B-F11CFAEA1F12}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="26370" yWindow="750" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>authors</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>paper_url</t>
+  </si>
+  <si>
+    <t>paper_publish_date</t>
+  </si>
+  <si>
+    <t>keywords</t>
+  </si>
+  <si>
+    <t>pip_vintage_primary_data</t>
+  </si>
+  <si>
+    <t>economy_excl_reason</t>
+  </si>
+  <si>
+    <t>aggregates_excl_reason</t>
+  </si>
+  <si>
+    <t>limitations</t>
+  </si>
+  <si>
+    <t>citation</t>
+  </si>
+  <si>
+    <t>Identifying the poor – Accounting for household economies of scale in global poverty estimates</t>
+  </si>
+  <si>
+    <t>Dean Jolliffe, Samuel Kofi Tetteh-Baah</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S0305750X24000639</t>
+  </si>
+  <si>
+    <t>Global poverty; Household economies of scale; Sustainable development goals</t>
+  </si>
+  <si>
+    <t>March 2023 PIP data</t>
+  </si>
+  <si>
+    <t>Nine countries are excluded because the data for these countries are reported in aggregate form (grouped data) and are not available at the unit-record level. These nine countries are: Australia, Canada, Germany, Israel, Japan, Republic of Korea, Taiwan-China, the United Kingdom and the United States.</t>
+  </si>
+  <si>
+    <t>All aggregates are included.</t>
+  </si>
+  <si>
+    <t>1. The paper adopts three approaches to setting the scaled poverty lines that incorporate economies of scale. The estimates available in the PIP Innovation Hub are based on the approach proposed by Martin Ravallion. See the paper for discussion on the three approaches to setting the scaled poverty lines. The estimates based on the other two approaches are not provided in the PIP Innovation Hub, but are available upon request._x000D_
+2. The estimates provided in the PIP Innovation Hub are exactly survey year estimates but for the 2019 reference year, relying on the closest survey data in time to 2019. When the latest available survey was conducted in a period prior to 2019, the poverty estimate is extrapolated from that survey. However, when the latest survey was conducted after 2019, the poverty estimate for 2019 is interpolated from the two closest surveys in time to 2019. For more details, see the PIP Methodology Handbook. Here is the link: https://datanalytics.worldbank.org/PIP-Methodology/lineupestimates.html</t>
+  </si>
+  <si>
+    <t>Jolliffe, D. and Tetteh-Baah, S.K., 2024. Identifying the poor–Accounting for household economies of scale in global poverty estimates. World Development, 179, p.106593.</t>
+  </si>
+  <si>
+    <t>Jolliffe and Tetteh-Baah (2024) incorporate economies of scale in household consumption into the estimation of global poverty. They use a constant-elasticity scale adjustment that divides total household welfare by the square-root of household size, the so-called square-root approach. This is contrasted to the current standard method of dividing welfare by household size, which is the per-capita approach.  The square-root approach is expected to be more consistent with household consumption patterns, as household public goods such as housing and consumer durables are shared among household members at limited or no marginal cost.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd HH:mm:ss UTC"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss\ \U\T\C"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -67,13 +142,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -111,7 +194,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -145,6 +228,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -179,9 +263,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -354,127 +439,87 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="20.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>authors</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>paper_url</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>paper_publish_date</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>keywords</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>pip_vintage_primary_data</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>economy_excl_reason</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>aggregates_excl_reason</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>limitations</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Identifying the poor – Accounting for household economies of scale in global poverty estimates</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Dean Jolliffe, Samuel Kofi Tetteh-Baah</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Short description of the methodology, including its purpose and scope. This should be approximately two sentences.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0305750X24000639</t>
-        </is>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
       </c>
       <c r="E2" s="2">
         <v>45474</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Global poverty; Household economies of scale; Sustainable development goals</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>March 2023 PIP data</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Nine countries are excluded because the data for these countries are reported in aggregate form (grouped data) and are not available at the unit-record level. These nine countries are: Australia, Canada, Germany, Israel, Japan, Republic of Korea, Taiwan-China, the United Kingdom and the United States.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>All aggregates are included.</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>1. The paper adopts three approaches to setting the scaled poverty lines that incorporate economies of scale. The estimates available in the PIP Innovation Hub are based on the approach proposed by Martin Ravallion. See the paper for discussion on the three approaches to setting the scaled poverty lines. The estimates based on the other two approaches are not provided in the PIP Innovation Hub, but are available upon request._x000D_
-2. The estimates provided in the PIP Innovation Hub are exactly survey year estimates but for the 2019 reference year, relying on the closest survey data in time to 2019. When the latest available survey was conducted in a period prior to 2019, the poverty estimate is extrapolated from that survey. However, when the latest survey was conducted after 2019, the poverty estimate for 2019 is interpolated from the two closest surveys in time to 2019. For more details, see the PIP Methodology Handbook. Here is the link: https://datanalytics.worldbank.org/PIP-Methodology/lineupestimates.html</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Jolliffe, D. and Tetteh-Baah, S.K., 2024. Identifying the poor–Accounting for household economies of scale in global poverty estimates. World Development, 179, p.106593.</t>
-        </is>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;R_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Official Use Only</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
--- a/inst/app/metadata/stettehbaah_2024-08-16.xlsx
+++ b/inst/app/metadata/stettehbaah_2024-08-16.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://worldbankgroup-my.sharepoint.com/personal/zprinsloo_worldbank_org/Documents/innovation_hub/InnovationHubDashboard/inst/app/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_6D68FDCE8F79A89360642C52EAAAD23310C181F4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{924F6C67-2211-4544-B55B-F11CFAEA1F12}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_6D68FDCE8F79A89360642C52EAAAD23310C181F4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{146F2A14-2170-4334-86CD-DF32A2FEF28D}"/>
   <bookViews>
-    <workbookView xWindow="26370" yWindow="750" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="53880" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -93,7 +93,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss\ \U\T\C"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -105,6 +105,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -127,17 +135,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -441,12 +452,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="5" max="5" width="20.7109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="20.7265625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -481,7 +492,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -491,7 +502,7 @@
       <c r="C2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E2" s="2">
@@ -517,6 +528,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{9BF06403-58DC-40FE-A2F8-7F5363678FE6}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter>&amp;R_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Official Use Only</oddFooter>
